--- a/samples/valorgrid-template/valorgrid-template-sp500-synthetic.xlsx
+++ b/samples/valorgrid-template/valorgrid-template-sp500-synthetic.xlsx
@@ -1,47 +1,218 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Movimientos" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Movimientos" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="63">
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Yahoo</t>
+  </si>
+  <si>
+    <t>Acciones</t>
+  </si>
+  <si>
+    <t>Precio</t>
+  </si>
+  <si>
+    <t>Divisa</t>
+  </si>
+  <si>
+    <t>FX a EUR</t>
+  </si>
+  <si>
+    <t>Valor EUR</t>
+  </si>
+  <si>
+    <t>Comision EUR</t>
+  </si>
+  <si>
+    <t>Referencia</t>
+  </si>
+  <si>
+    <t>compra</t>
+  </si>
+  <si>
+    <t>15/01/2025</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>185.50</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>sample-sp500-001</t>
+  </si>
+  <si>
+    <t>01/02/2025</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>420.30</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>sample-sp500-002</t>
+  </si>
+  <si>
+    <t>10/03/2025</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>890.75</t>
+  </si>
+  <si>
+    <t>6555.92</t>
+  </si>
+  <si>
+    <t>1.50</t>
+  </si>
+  <si>
+    <t>sample-sp500-003</t>
+  </si>
+  <si>
+    <t>20/03/2025</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>62.40</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>sample-sp500-004</t>
+  </si>
+  <si>
+    <t>05/04/2025</t>
+  </si>
+  <si>
+    <t>JNJ</t>
+  </si>
+  <si>
+    <t>158.30</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>sample-sp500-005</t>
+  </si>
+  <si>
+    <t>venta</t>
+  </si>
+  <si>
+    <t>15/05/2025</t>
+  </si>
+  <si>
+    <t>192.80</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>sample-sp500-006</t>
+  </si>
+  <si>
+    <t>01/06/2025</t>
+  </si>
+  <si>
+    <t>65.10</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>sample-sp500-007</t>
+  </si>
+  <si>
+    <t>10/06/2025</t>
+  </si>
+  <si>
+    <t>XOM</t>
+  </si>
+  <si>
+    <t>115.20</t>
+  </si>
+  <si>
+    <t>1572.48</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>sample-sp500-008</t>
+  </si>
+  <si>
+    <t>20/07/2025</t>
+  </si>
+  <si>
+    <t>448.75</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>sample-sp500-009</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,13 +236,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,344 +575,365 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="1" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tipo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Fecha</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Ticker</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Acciones</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Precio</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Divisa</v>
-      </c>
-      <c r="G1" t="str">
-        <v>FX a EUR</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Valor EUR</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Comision EUR</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Referencia</v>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>compra</v>
-      </c>
-      <c r="B2" t="str">
-        <v>15/01/2025</v>
-      </c>
-      <c r="C2" t="str">
-        <v>AAPL</v>
-      </c>
-      <c r="D2" t="str">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2">
         <v>10</v>
       </c>
-      <c r="E2" t="str">
-        <v>185.50</v>
-      </c>
-      <c r="F2" t="str">
-        <v>USD</v>
-      </c>
-      <c r="G2" t="str">
-        <v>0.92</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>1.25</v>
-      </c>
-      <c r="J2" t="str">
-        <v>sample-sp500-001</v>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>compra</v>
-      </c>
-      <c r="B3" t="str">
-        <v>01/02/2025</v>
-      </c>
-      <c r="C3" t="str">
-        <v>MSFT</v>
-      </c>
-      <c r="D3" t="str">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="E3" t="str">
-        <v>420.30</v>
-      </c>
-      <c r="F3" t="str">
-        <v>USD</v>
-      </c>
-      <c r="G3" t="str">
-        <v>0.92</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>0.80</v>
-      </c>
-      <c r="J3" t="str">
-        <v>sample-sp500-002</v>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>compra</v>
-      </c>
-      <c r="B4" t="str">
-        <v>10/03/2025</v>
-      </c>
-      <c r="C4" t="str">
-        <v>NVDA</v>
-      </c>
-      <c r="D4" t="str">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4">
         <v>8</v>
       </c>
-      <c r="E4" t="str">
-        <v>890.75</v>
-      </c>
-      <c r="F4" t="str">
-        <v>USD</v>
-      </c>
-      <c r="G4" t="str">
-        <v>0.92</v>
-      </c>
-      <c r="H4" t="str">
-        <v>6555.92</v>
-      </c>
-      <c r="I4" t="str">
-        <v>1.50</v>
-      </c>
-      <c r="J4" t="str">
-        <v>sample-sp500-003</v>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>compra</v>
-      </c>
-      <c r="B5" t="str">
-        <v>20/03/2025</v>
-      </c>
-      <c r="C5" t="str">
-        <v>KO</v>
-      </c>
-      <c r="D5" t="str">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5">
         <v>25</v>
       </c>
-      <c r="E5" t="str">
-        <v>62.40</v>
-      </c>
-      <c r="F5" t="str">
-        <v>USD</v>
-      </c>
-      <c r="G5" t="str">
-        <v>0.92</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>0</v>
-      </c>
-      <c r="J5" t="str">
-        <v>sample-sp500-004</v>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>compra</v>
-      </c>
-      <c r="B6" t="str">
-        <v>05/04/2025</v>
-      </c>
-      <c r="C6" t="str">
-        <v>JNJ</v>
-      </c>
-      <c r="D6" t="str">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6">
         <v>12</v>
       </c>
-      <c r="E6" t="str">
-        <v>158.30</v>
-      </c>
-      <c r="F6" t="str">
-        <v>USD</v>
-      </c>
-      <c r="G6" t="str">
-        <v>0.92</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>0.60</v>
-      </c>
-      <c r="J6" t="str">
-        <v>sample-sp500-005</v>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>venta</v>
-      </c>
-      <c r="B7" t="str">
-        <v>15/05/2025</v>
-      </c>
-      <c r="C7" t="str">
-        <v>AAPL</v>
-      </c>
-      <c r="D7" t="str">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7">
         <v>4</v>
       </c>
-      <c r="E7" t="str">
-        <v>192.80</v>
-      </c>
-      <c r="F7" t="str">
-        <v>USD</v>
-      </c>
-      <c r="G7" t="str">
-        <v>0.91</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>0.95</v>
-      </c>
-      <c r="J7" t="str">
-        <v>sample-sp500-006</v>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v>01/06/2025</v>
-      </c>
-      <c r="C8" t="str">
-        <v>KO</v>
-      </c>
-      <c r="D8" t="str">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8">
         <v>-5</v>
       </c>
-      <c r="E8" t="str">
-        <v>65.10</v>
-      </c>
-      <c r="F8" t="str">
-        <v>USD</v>
-      </c>
-      <c r="G8" t="str">
-        <v>0.90</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>0.25</v>
-      </c>
-      <c r="J8" t="str">
-        <v>sample-sp500-007</v>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>compra</v>
-      </c>
-      <c r="B9" t="str">
-        <v>10/06/2025</v>
-      </c>
-      <c r="C9" t="str">
-        <v>XOM</v>
-      </c>
-      <c r="D9" t="str">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9">
         <v>15</v>
       </c>
-      <c r="E9" t="str">
-        <v>115.20</v>
-      </c>
-      <c r="F9" t="str">
-        <v>USD</v>
-      </c>
-      <c r="G9" t="str">
-        <v>0.91</v>
-      </c>
-      <c r="H9" t="str">
-        <v>1572.48</v>
-      </c>
-      <c r="I9" t="str">
-        <v>0.45</v>
-      </c>
-      <c r="J9" t="str">
-        <v>sample-sp500-008</v>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>venta</v>
-      </c>
-      <c r="B10" t="str">
-        <v>20/07/2025</v>
-      </c>
-      <c r="C10" t="str">
-        <v>MSFT</v>
-      </c>
-      <c r="D10" t="str">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10">
         <v>2</v>
       </c>
-      <c r="E10" t="str">
-        <v>448.75</v>
-      </c>
-      <c r="F10" t="str">
-        <v>USD</v>
-      </c>
-      <c r="G10" t="str">
-        <v>0.93</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>0.70</v>
-      </c>
-      <c r="J10" t="str">
-        <v>sample-sp500-009</v>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>